--- a/artfynd/A 55142-2025 artfynd.xlsx
+++ b/artfynd/A 55142-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,224 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130010099</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572705</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6423781</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130010103</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572603</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6423916</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55142-2025 artfynd.xlsx
+++ b/artfynd/A 55142-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,6 +1005,111 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130020562</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92188</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572647</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6423858</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55142-2025 artfynd.xlsx
+++ b/artfynd/A 55142-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>130020562</v>
       </c>
       <c r="B5" t="n">
-        <v>92188</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55142-2025 artfynd.xlsx
+++ b/artfynd/A 55142-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>130010099</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>130010103</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130020562</v>
       </c>
       <c r="B5" t="n">
-        <v>92189</v>
+        <v>92206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55142-2025 artfynd.xlsx
+++ b/artfynd/A 55142-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>130020562</v>
       </c>
       <c r="B5" t="n">
-        <v>92222</v>
+        <v>92224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55142-2025 artfynd.xlsx
+++ b/artfynd/A 55142-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>130010099</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>130010103</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130020562</v>
       </c>
       <c r="B5" t="n">
-        <v>92224</v>
+        <v>92311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55142-2025 artfynd.xlsx
+++ b/artfynd/A 55142-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116945131</v>
+        <v>116945044</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -726,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572641</v>
+        <v>572605</v>
       </c>
       <c r="R2" t="n">
-        <v>6423866</v>
+        <v>6423869</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +753,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt på 2 närbelägna asplågor. Återfynd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130010099</v>
+        <v>130011473</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,49 +796,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 55142, St Skälhem, Sm</t>
+          <t>Jansbo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572705</v>
+        <v>572608</v>
       </c>
       <c r="R3" t="n">
-        <v>6423781</v>
+        <v>6423863</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,84 +865,81 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På två barklösa asplågor</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130010103</v>
+        <v>116289270</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 55142, St Skälhem, Sm</t>
+          <t>Jansbo, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572603</v>
+        <v>572605</v>
       </c>
       <c r="R4" t="n">
-        <v>6423916</v>
+        <v>6423869</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,12 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera tickor på två asp lågor bredvid varandra.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,28 +982,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jan Aronsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+          <t>Jan Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130020562</v>
+        <v>116945131</v>
       </c>
       <c r="B5" t="n">
-        <v>92311</v>
+        <v>92497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,7 +1029,11 @@
           <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1045,14 +1043,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 55142, St Skälhem, Sm</t>
+          <t>Jansbo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572647</v>
+        <v>572641</v>
       </c>
       <c r="R5" t="n">
-        <v>6423858</v>
+        <v>6423866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,15 +1098,1400 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130010025</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572633</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6423842</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130010037</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572646</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6423836</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130020562</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572647</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6423858</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130010459</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572638</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6423862</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130010468</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572624</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6423873</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130010060</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572659</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6423892</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114953145</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>572563</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6423965</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130010103</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>572603</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6423916</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>116944992</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jansbo, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>572643</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6423835</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>116945152</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jansbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572635</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6423838</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>116945021</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jansbo, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572624</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6423877</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>116945169</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jansbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>572635</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6423838</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130010099</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 55142, St Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>572705</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6423781</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
